--- a/data-manipulation-scripts/sheets-cleanup/sheets/GUIDO NOVO 18_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/GUIDO NOVO 18_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -31,7 +31,10 @@
     <t>GUIDO CINZA XRE300 2010 A 2015</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>7908285444300</t>
+  </si>
+  <si>
+    <t>GUIDO PROTORK CROMADO CG TITAN START150 160 2016 A 2019/ FAN125 150 2014</t>
   </si>
 </sst>
 </file>
@@ -345,10 +348,14 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>75.0</v>
       </c>
     </row>
     <row r="4">
